--- a/results/GSE186332/selinexor_clear_response_cohort.xlsx
+++ b/results/GSE186332/selinexor_clear_response_cohort.xlsx
@@ -456,7 +456,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>-0.09053496729843569</v>
+        <v>-0.09053496729843558</v>
       </c>
     </row>
     <row r="5">
@@ -466,7 +466,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-0.1669232286961848</v>
+        <v>-0.1669232286961846</v>
       </c>
     </row>
     <row r="6">
@@ -597,7 +597,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.3035692459935511</v>
+        <v>0.3035692459935508</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -640,7 +640,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-0.09053496729843569</v>
+        <v>-0.09053496729843558</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -898,7 +898,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-0.5012702603247939</v>
+        <v>-0.5012702603247938</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -941,7 +941,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>-0.1669232286961848</v>
+        <v>-0.1669232286961846</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -984,7 +984,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>-0.3855596391587646</v>
+        <v>-0.3855596391587647</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1113,7 +1113,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.1197571205511969</v>
+        <v>0.1197571205511967</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1156,7 +1156,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>-0.3263959549847679</v>
+        <v>-0.3263959549847678</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -1242,7 +1242,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>-0.09783912785934074</v>
+        <v>-0.09783912785934062</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -1457,7 +1457,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>-0.01875336389815385</v>
+        <v>-0.0187533638981538</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -1500,7 +1500,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.2386366811022367</v>
+        <v>0.2386366811022368</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -1629,7 +1629,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.2518575374672229</v>
+        <v>0.2518575374672231</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -1715,7 +1715,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>-0.2729567360682781</v>
+        <v>-0.272956736068278</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>

--- a/results/GSE186332/selinexor_clear_response_cohort.xlsx
+++ b/results/GSE186332/selinexor_clear_response_cohort.xlsx
@@ -456,7 +456,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>-0.09053496729843558</v>
+        <v>-0.09053496729843552</v>
       </c>
     </row>
     <row r="5">
@@ -466,7 +466,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-0.1669232286961846</v>
+        <v>-0.1669232286961848</v>
       </c>
     </row>
     <row r="6">
@@ -597,7 +597,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.3035692459935508</v>
+        <v>0.303569245993551</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -640,7 +640,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-0.09053496729843558</v>
+        <v>-0.09053496729843552</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -683,7 +683,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>-0.0006384040292134463</v>
+        <v>-0.0006384040292133353</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -769,7 +769,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-0.2540539747143987</v>
+        <v>-0.2540539747143988</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -812,7 +812,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.190930439496977</v>
+        <v>0.1909304394969769</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -941,7 +941,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>-0.1669232286961846</v>
+        <v>-0.1669232286961848</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -984,7 +984,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>-0.3855596391587647</v>
+        <v>-0.3855596391587646</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1070,7 +1070,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.285845185822498</v>
+        <v>0.2858451858224979</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1113,7 +1113,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.1197571205511967</v>
+        <v>0.1197571205511969</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1199,7 +1199,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>-0.1405419733734229</v>
+        <v>-0.1405419733734231</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -1242,7 +1242,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>-0.09783912785934062</v>
+        <v>-0.09783912785934074</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -1414,7 +1414,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.001004040388167093</v>
+        <v>0.001004040388167204</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -1457,7 +1457,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>-0.0187533638981538</v>
+        <v>-0.01875336389815396</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -1500,7 +1500,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.2386366811022368</v>
+        <v>0.2386366811022366</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -1543,7 +1543,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>-0.1253328976907889</v>
+        <v>-0.125332897690789</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -1629,7 +1629,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.2518575374672231</v>
+        <v>0.2518575374672232</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -1715,7 +1715,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>-0.272956736068278</v>
+        <v>-0.2729567360682781</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -1801,7 +1801,7 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-0.3481914504932407</v>
+        <v>-0.3481914504932406</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>

--- a/results/GSE186332/selinexor_clear_response_cohort.xlsx
+++ b/results/GSE186332/selinexor_clear_response_cohort.xlsx
@@ -456,7 +456,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>-0.09053496729843552</v>
+        <v>-0.09053496729843558</v>
       </c>
     </row>
     <row r="5">
@@ -466,7 +466,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-0.1669232286961848</v>
+        <v>-0.1669232286961847</v>
       </c>
     </row>
     <row r="6">
@@ -597,7 +597,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.303569245993551</v>
+        <v>0.3035692459935509</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -640,7 +640,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-0.09053496729843552</v>
+        <v>-0.09053496729843558</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -683,7 +683,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>-0.0006384040292133353</v>
+        <v>-0.0006384040292134463</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -726,7 +726,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.3490853798274803</v>
+        <v>0.3490853798274802</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -769,7 +769,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-0.2540539747143988</v>
+        <v>-0.2540539747143989</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -855,7 +855,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-0.3621064211877677</v>
+        <v>-0.3621064211877676</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -898,7 +898,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-0.5012702603247938</v>
+        <v>-0.5012702603247937</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -941,7 +941,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>-0.1669232286961848</v>
+        <v>-0.1669232286961847</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1027,7 +1027,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.05396025482033245</v>
+        <v>0.0539602548203324</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1070,7 +1070,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.2858451858224979</v>
+        <v>0.285845185822498</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1199,7 +1199,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>-0.1405419733734231</v>
+        <v>-0.1405419733734229</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -1242,7 +1242,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>-0.09783912785934074</v>
+        <v>-0.09783912785934068</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -1371,7 +1371,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>-0.2353514648807942</v>
+        <v>-0.2353514648807941</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -1414,7 +1414,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.001004040388167204</v>
+        <v>0.001004040388167038</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -1457,7 +1457,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>-0.01875336389815396</v>
+        <v>-0.01875336389815391</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -1500,7 +1500,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.2386366811022366</v>
+        <v>0.2386366811022367</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -1543,7 +1543,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>-0.125332897690789</v>
+        <v>-0.1253328976907889</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -1629,7 +1629,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.2518575374672232</v>
+        <v>0.251857537467223</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -1672,7 +1672,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>-0.1656100261516483</v>
+        <v>-0.1656100261516482</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -1801,7 +1801,7 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-0.3481914504932406</v>
+        <v>-0.3481914504932407</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>

--- a/results/GSE186332/selinexor_clear_response_cohort.xlsx
+++ b/results/GSE186332/selinexor_clear_response_cohort.xlsx
@@ -456,7 +456,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>-0.09053496729843558</v>
+        <v>-0.09053496729843569</v>
       </c>
     </row>
     <row r="5">
@@ -466,7 +466,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-0.1669232286961847</v>
+        <v>-0.1669232286961848</v>
       </c>
     </row>
     <row r="6">
@@ -597,7 +597,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.3035692459935509</v>
+        <v>0.303569245993551</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -640,7 +640,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-0.09053496729843558</v>
+        <v>-0.09053496729843569</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -726,7 +726,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.3490853798274802</v>
+        <v>0.3490853798274803</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -769,7 +769,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-0.2540539747143989</v>
+        <v>-0.2540539747143988</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -812,7 +812,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.1909304394969769</v>
+        <v>0.190930439496977</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -898,7 +898,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-0.5012702603247937</v>
+        <v>-0.5012702603247938</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -941,7 +941,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>-0.1669232286961847</v>
+        <v>-0.1669232286961848</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1027,7 +1027,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.0539602548203324</v>
+        <v>0.05396025482033245</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1113,7 +1113,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.1197571205511969</v>
+        <v>0.119757120551197</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1199,7 +1199,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>-0.1405419733734229</v>
+        <v>-0.1405419733734231</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -1242,7 +1242,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>-0.09783912785934068</v>
+        <v>-0.09783912785934062</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -1371,7 +1371,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>-0.2353514648807941</v>
+        <v>-0.2353514648807942</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -1457,7 +1457,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>-0.01875336389815391</v>
+        <v>-0.01875336389815396</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -1543,7 +1543,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>-0.1253328976907889</v>
+        <v>-0.125332897690789</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -1629,7 +1629,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.251857537467223</v>
+        <v>0.2518575374672233</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -1715,7 +1715,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>-0.2729567360682781</v>
+        <v>-0.272956736068278</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>

--- a/results/GSE186332/selinexor_clear_response_cohort.xlsx
+++ b/results/GSE186332/selinexor_clear_response_cohort.xlsx
@@ -456,7 +456,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>-0.09053496729843569</v>
+        <v>-0.09053496729843552</v>
       </c>
     </row>
     <row r="5">
@@ -597,7 +597,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.303569245993551</v>
+        <v>0.3035692459935511</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -640,7 +640,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-0.09053496729843569</v>
+        <v>-0.09053496729843552</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -683,7 +683,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>-0.0006384040292134463</v>
+        <v>-0.0006384040292133353</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -812,7 +812,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.190930439496977</v>
+        <v>0.1909304394969768</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -855,7 +855,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-0.3621064211877676</v>
+        <v>-0.3621064211877677</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -898,7 +898,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-0.5012702603247938</v>
+        <v>-0.5012702603247936</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1027,7 +1027,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.05396025482033245</v>
+        <v>0.05396025482033234</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1070,7 +1070,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.285845185822498</v>
+        <v>0.2858451858224981</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1199,7 +1199,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>-0.1405419733734231</v>
+        <v>-0.1405419733734229</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -1543,7 +1543,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>-0.125332897690789</v>
+        <v>-0.1253328976907889</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -1586,7 +1586,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>-0.172338913748451</v>
+        <v>-0.1723389137484508</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -1629,7 +1629,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.2518575374672233</v>
+        <v>0.251857537467223</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -1672,7 +1672,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>-0.1656100261516482</v>
+        <v>-0.1656100261516483</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -1844,7 +1844,7 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-0.329928948359771</v>
+        <v>-0.3299289483597709</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
